--- a/data/ihlp_core_data.xlsx
+++ b/data/ihlp_core_data.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="8_{247AF56F-93CC-4D6A-B27C-89B9CEAD7EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D61DED-EC20-471F-B6E3-E64540BA5924}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="8_{247AF56F-93CC-4D6A-B27C-89B9CEAD7EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1789E1C-046B-4EE6-8E2A-649459D80143}"/>
   <bookViews>
-    <workbookView xWindow="-26265" yWindow="-120" windowWidth="26385" windowHeight="14925" firstSheet="3" activeTab="9" xr2:uid="{6B55D013-80A8-49D2-A1D1-956E5A60CC14}"/>
+    <workbookView xWindow="4290" yWindow="3735" windowWidth="21600" windowHeight="11700" xr2:uid="{6B55D013-80A8-49D2-A1D1-956E5A60CC14}"/>
   </bookViews>
   <sheets>
-    <sheet name="ihlp2525cz01" sheetId="8" r:id="rId1"/>
-    <sheet name="ihlp2525cz11" sheetId="9" r:id="rId2"/>
-    <sheet name="ihlp3232cz01" sheetId="10" r:id="rId3"/>
-    <sheet name="ihlp3232cz11" sheetId="11" r:id="rId4"/>
-    <sheet name="ihlp3232dz01" sheetId="6" r:id="rId5"/>
-    <sheet name="ihlp3232dz11" sheetId="7" r:id="rId6"/>
-    <sheet name="ihlp4040dz01" sheetId="1" r:id="rId7"/>
-    <sheet name="ihlp4040dz11" sheetId="2" r:id="rId8"/>
-    <sheet name="ihlp5050ce01" sheetId="3" r:id="rId9"/>
-    <sheet name="ihlp5050ez01" sheetId="12" r:id="rId10"/>
-    <sheet name="ihlp6767dz01" sheetId="4" r:id="rId11"/>
-    <sheet name="ihlp6767dz11" sheetId="5" r:id="rId12"/>
+    <sheet name="ihlp2525bz01" sheetId="13" r:id="rId1"/>
+    <sheet name="ihlp2525cz01" sheetId="8" r:id="rId2"/>
+    <sheet name="ihlp2525cz11" sheetId="9" r:id="rId3"/>
+    <sheet name="ihlp3232cz01" sheetId="10" r:id="rId4"/>
+    <sheet name="ihlp3232cz11" sheetId="11" r:id="rId5"/>
+    <sheet name="ihlp3232dz01" sheetId="6" r:id="rId6"/>
+    <sheet name="ihlp3232dz11" sheetId="7" r:id="rId7"/>
+    <sheet name="ihlp4040dz01" sheetId="1" r:id="rId8"/>
+    <sheet name="ihlp4040dz11" sheetId="2" r:id="rId9"/>
+    <sheet name="ihlp5050ce01" sheetId="3" r:id="rId10"/>
+    <sheet name="ihlp5050ez01" sheetId="12" r:id="rId11"/>
+    <sheet name="ihlp6767dz01" sheetId="4" r:id="rId12"/>
+    <sheet name="ihlp6767dz11" sheetId="5" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="28">
   <si>
     <t>Rth</t>
   </si>
@@ -128,6 +129,9 @@
   </si>
   <si>
     <t>ihlp5050ez01</t>
+  </si>
+  <si>
+    <t>ihlp2525bz01</t>
   </si>
 </sst>
 </file>
@@ -491,6 +495,3925 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD5E1D3-F2A4-4470-9F05-7C4070FC0DCF}">
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.1</v>
+      </c>
+      <c r="B2">
+        <v>1.5E-3</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>25.68</v>
+      </c>
+      <c r="F2">
+        <v>1.56</v>
+      </c>
+      <c r="G2">
+        <v>0.13</v>
+      </c>
+      <c r="H2">
+        <v>3.13</v>
+      </c>
+      <c r="I2">
+        <v>7.1000000000000002E-4</v>
+      </c>
+      <c r="J2">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K2">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N2">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O2">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.22</v>
+      </c>
+      <c r="B3">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="C3">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>27.1</v>
+      </c>
+      <c r="F3">
+        <v>1.48</v>
+      </c>
+      <c r="G3">
+        <v>0.24</v>
+      </c>
+      <c r="H3">
+        <v>3.46</v>
+      </c>
+      <c r="I3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K3">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N3">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.33</v>
+      </c>
+      <c r="B4">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>28.91</v>
+      </c>
+      <c r="F4">
+        <v>1.38</v>
+      </c>
+      <c r="G4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H4">
+        <v>3.02</v>
+      </c>
+      <c r="I4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J4">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K4">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N4">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O4">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.47</v>
+      </c>
+      <c r="B5">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>13.5</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31.7</v>
+      </c>
+      <c r="F5">
+        <v>1.26</v>
+      </c>
+      <c r="G5">
+        <v>0.33</v>
+      </c>
+      <c r="H5">
+        <v>2.78</v>
+      </c>
+      <c r="I5">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K5">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N5">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O5">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.68</v>
+      </c>
+      <c r="B6">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>32.93</v>
+      </c>
+      <c r="F6">
+        <v>1.21</v>
+      </c>
+      <c r="G6">
+        <v>0.41</v>
+      </c>
+      <c r="H6">
+        <v>2.8</v>
+      </c>
+      <c r="I6">
+        <v>1.33E-3</v>
+      </c>
+      <c r="J6">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K6">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N6">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O6">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.82</v>
+      </c>
+      <c r="B7">
+        <v>1.06E-2</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="F7">
+        <v>1.22</v>
+      </c>
+      <c r="G7">
+        <v>0.49</v>
+      </c>
+      <c r="H7">
+        <v>3.29</v>
+      </c>
+      <c r="I7">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J7">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K7">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N7">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O7">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>32.67</v>
+      </c>
+      <c r="F8">
+        <v>1.22</v>
+      </c>
+      <c r="G8">
+        <v>0.69</v>
+      </c>
+      <c r="H8">
+        <v>5.23</v>
+      </c>
+      <c r="I8">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J8">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N8">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O8">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.5</v>
+      </c>
+      <c r="B9">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>33.31</v>
+      </c>
+      <c r="F9">
+        <v>1.2</v>
+      </c>
+      <c r="G9">
+        <v>0.92</v>
+      </c>
+      <c r="H9">
+        <v>6.01</v>
+      </c>
+      <c r="I9">
+        <v>1.07E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K9">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N9">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10">
+        <v>2.3E-2</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>29.3</v>
+      </c>
+      <c r="F10">
+        <v>1.37</v>
+      </c>
+      <c r="G10">
+        <v>1.06</v>
+      </c>
+      <c r="H10">
+        <v>6.15</v>
+      </c>
+      <c r="I10">
+        <v>1.07E-3</v>
+      </c>
+      <c r="J10">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K10">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N10">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O10">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3.3</v>
+      </c>
+      <c r="B11">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>37.99</v>
+      </c>
+      <c r="F11">
+        <v>1.05</v>
+      </c>
+      <c r="G11">
+        <v>1.39</v>
+      </c>
+      <c r="H11">
+        <v>6.03</v>
+      </c>
+      <c r="I11">
+        <v>3.5400000000000002E-3</v>
+      </c>
+      <c r="J11">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K11">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N11">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4.7</v>
+      </c>
+      <c r="B12">
+        <v>4.5199999999999997E-2</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>37.869999999999997</v>
+      </c>
+      <c r="F12">
+        <v>1.06</v>
+      </c>
+      <c r="G12">
+        <v>1.27</v>
+      </c>
+      <c r="H12">
+        <v>3.87</v>
+      </c>
+      <c r="I12">
+        <v>3.5400000000000002E-3</v>
+      </c>
+      <c r="J12">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K12">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N12">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O12">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>6.8</v>
+      </c>
+      <c r="B13">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="C13">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>39.03</v>
+      </c>
+      <c r="F13">
+        <v>1.02</v>
+      </c>
+      <c r="G13">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="H13">
+        <v>5.82</v>
+      </c>
+      <c r="I13">
+        <v>3.0599999999999998E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K13">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N13">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O13">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B14">
+        <v>8.4199999999999997E-2</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>45.74</v>
+      </c>
+      <c r="F14">
+        <v>0.87</v>
+      </c>
+      <c r="G14">
+        <v>1.98</v>
+      </c>
+      <c r="H14">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I14">
+        <v>3.0599999999999998E-3</v>
+      </c>
+      <c r="J14">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K14">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N14">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O14">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>0.11559999999999999</v>
+      </c>
+      <c r="C15">
+        <v>2.5</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>47.98</v>
+      </c>
+      <c r="F15">
+        <v>0.83</v>
+      </c>
+      <c r="G15">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="H15">
+        <v>7.08</v>
+      </c>
+      <c r="I15">
+        <v>2.81E-3</v>
+      </c>
+      <c r="J15">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15">
+        <v>6.7240000000000002</v>
+      </c>
+      <c r="N15">
+        <v>7.2409999999999997</v>
+      </c>
+      <c r="O15">
+        <v>2.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCC0EA7-1C1A-400A-B5A7-4CD8402EAE42}">
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.1</v>
+      </c>
+      <c r="B2">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="C2">
+        <v>43</v>
+      </c>
+      <c r="D2">
+        <v>84</v>
+      </c>
+      <c r="E2">
+        <v>23.43</v>
+      </c>
+      <c r="F2">
+        <v>1.71</v>
+      </c>
+      <c r="G2">
+        <v>0.09</v>
+      </c>
+      <c r="H2">
+        <v>2.38</v>
+      </c>
+      <c r="I2">
+        <v>1.2800000000000001E-3</v>
+      </c>
+      <c r="J2">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K2">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>12.9</v>
+      </c>
+      <c r="N2">
+        <v>13.58</v>
+      </c>
+      <c r="O2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.15</v>
+      </c>
+      <c r="B3">
+        <v>1E-3</v>
+      </c>
+      <c r="C3">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>75</v>
+      </c>
+      <c r="E3">
+        <v>20.62</v>
+      </c>
+      <c r="F3">
+        <v>1.94</v>
+      </c>
+      <c r="G3">
+        <v>0.27</v>
+      </c>
+      <c r="H3">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="I3">
+        <v>1.2800000000000001E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K3">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>12.9</v>
+      </c>
+      <c r="N3">
+        <v>13.58</v>
+      </c>
+      <c r="O3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.22</v>
+      </c>
+      <c r="B4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="C4">
+        <v>38.5</v>
+      </c>
+      <c r="D4">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>21.26</v>
+      </c>
+      <c r="F4">
+        <v>1.88</v>
+      </c>
+      <c r="G4">
+        <v>0.71</v>
+      </c>
+      <c r="H4">
+        <v>32.14</v>
+      </c>
+      <c r="I4">
+        <v>1.2800000000000001E-3</v>
+      </c>
+      <c r="J4">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K4">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>12.9</v>
+      </c>
+      <c r="N4">
+        <v>13.58</v>
+      </c>
+      <c r="O4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.33</v>
+      </c>
+      <c r="B5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="C5">
+        <v>36.5</v>
+      </c>
+      <c r="D5">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0.8</v>
+      </c>
+      <c r="H5">
+        <v>23.86</v>
+      </c>
+      <c r="I5">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K5">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5">
+        <v>12.9</v>
+      </c>
+      <c r="N5">
+        <v>13.58</v>
+      </c>
+      <c r="O5">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.47</v>
+      </c>
+      <c r="B6">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>55</v>
+      </c>
+      <c r="E6">
+        <v>21.16</v>
+      </c>
+      <c r="F6">
+        <v>1.89</v>
+      </c>
+      <c r="G6">
+        <v>0.86</v>
+      </c>
+      <c r="H6">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="I6">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="J6">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K6">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6">
+        <v>12.9</v>
+      </c>
+      <c r="N6">
+        <v>13.58</v>
+      </c>
+      <c r="O6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.6</v>
+      </c>
+      <c r="B7">
+        <v>1.8E-3</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>22.9</v>
+      </c>
+      <c r="F7">
+        <v>1.75</v>
+      </c>
+      <c r="G7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="H7">
+        <v>25.74</v>
+      </c>
+      <c r="I7">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="J7">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K7">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7">
+        <v>12.9</v>
+      </c>
+      <c r="N7">
+        <v>13.58</v>
+      </c>
+      <c r="O7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.68</v>
+      </c>
+      <c r="B8">
+        <v>2.3E-3</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>19.22</v>
+      </c>
+      <c r="F8">
+        <v>2.08</v>
+      </c>
+      <c r="G8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H8">
+        <v>24.57</v>
+      </c>
+      <c r="I8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="J8">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8">
+        <v>12.9</v>
+      </c>
+      <c r="N8">
+        <v>13.58</v>
+      </c>
+      <c r="O8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.82</v>
+      </c>
+      <c r="B9">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>21.33</v>
+      </c>
+      <c r="F9">
+        <v>1.88</v>
+      </c>
+      <c r="G9">
+        <v>1.51</v>
+      </c>
+      <c r="H9">
+        <v>35.19</v>
+      </c>
+      <c r="I9">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K9">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9">
+        <v>12.9</v>
+      </c>
+      <c r="N9">
+        <v>13.58</v>
+      </c>
+      <c r="O9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>3.3E-3</v>
+      </c>
+      <c r="C10">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>18.239999999999998</v>
+      </c>
+      <c r="F10">
+        <v>2.19</v>
+      </c>
+      <c r="G10">
+        <v>1.32</v>
+      </c>
+      <c r="H10">
+        <v>21.69</v>
+      </c>
+      <c r="I10">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="J10">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K10">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10">
+        <v>12.9</v>
+      </c>
+      <c r="N10">
+        <v>13.58</v>
+      </c>
+      <c r="O10">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1.5</v>
+      </c>
+      <c r="B11">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <v>18.829999999999998</v>
+      </c>
+      <c r="F11">
+        <v>2.12</v>
+      </c>
+      <c r="G11">
+        <v>2.25</v>
+      </c>
+      <c r="H11">
+        <v>38.6</v>
+      </c>
+      <c r="I11">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J11">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K11">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11">
+        <v>12.9</v>
+      </c>
+      <c r="N11">
+        <v>13.58</v>
+      </c>
+      <c r="O11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1.8</v>
+      </c>
+      <c r="B12">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="C12">
+        <v>16.5</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>19.59</v>
+      </c>
+      <c r="F12">
+        <v>2.04</v>
+      </c>
+      <c r="G12">
+        <v>1.55</v>
+      </c>
+      <c r="H12">
+        <v>14.19</v>
+      </c>
+      <c r="I12">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="J12">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K12">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12">
+        <v>12.9</v>
+      </c>
+      <c r="N12">
+        <v>13.58</v>
+      </c>
+      <c r="O12">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="F13">
+        <v>2.13</v>
+      </c>
+      <c r="G13">
+        <v>2.1</v>
+      </c>
+      <c r="H13">
+        <v>31.39</v>
+      </c>
+      <c r="I13">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K13">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13">
+        <v>12.9</v>
+      </c>
+      <c r="N13">
+        <v>13.58</v>
+      </c>
+      <c r="O13">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>3.3</v>
+      </c>
+      <c r="B14">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
+      <c r="E14">
+        <v>21.88</v>
+      </c>
+      <c r="F14">
+        <v>1.83</v>
+      </c>
+      <c r="G14">
+        <v>2.71</v>
+      </c>
+      <c r="H14">
+        <v>25.18</v>
+      </c>
+      <c r="I14">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="J14">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K14">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14">
+        <v>12.9</v>
+      </c>
+      <c r="N14">
+        <v>13.58</v>
+      </c>
+      <c r="O14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4.7</v>
+      </c>
+      <c r="B15">
+        <v>1.43E-2</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>24.24</v>
+      </c>
+      <c r="F15">
+        <v>1.65</v>
+      </c>
+      <c r="G15">
+        <v>3.51</v>
+      </c>
+      <c r="H15">
+        <v>28.52</v>
+      </c>
+      <c r="I15">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="J15">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15">
+        <v>12.9</v>
+      </c>
+      <c r="N15">
+        <v>13.58</v>
+      </c>
+      <c r="O15">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5.6</v>
+      </c>
+      <c r="B16">
+        <v>1.83E-2</v>
+      </c>
+      <c r="C16">
+        <v>9.5</v>
+      </c>
+      <c r="D16">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>20.99</v>
+      </c>
+      <c r="F16">
+        <v>1.91</v>
+      </c>
+      <c r="G16">
+        <v>4.33</v>
+      </c>
+      <c r="H16">
+        <v>34.659999999999997</v>
+      </c>
+      <c r="I16">
+        <v>6.9699999999999996E-3</v>
+      </c>
+      <c r="J16">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K16">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16">
+        <v>12.9</v>
+      </c>
+      <c r="N16">
+        <v>13.58</v>
+      </c>
+      <c r="O16">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>6.8</v>
+      </c>
+      <c r="B17">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>18</v>
+      </c>
+      <c r="E17">
+        <v>21.61</v>
+      </c>
+      <c r="F17">
+        <v>1.85</v>
+      </c>
+      <c r="G17">
+        <v>3.86</v>
+      </c>
+      <c r="H17">
+        <v>25.1</v>
+      </c>
+      <c r="I17">
+        <v>6.9699999999999996E-3</v>
+      </c>
+      <c r="J17">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K17">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17">
+        <v>12.9</v>
+      </c>
+      <c r="N17">
+        <v>13.58</v>
+      </c>
+      <c r="O17">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B18">
+        <v>2.46E-2</v>
+      </c>
+      <c r="C18">
+        <v>8.5</v>
+      </c>
+      <c r="D18">
+        <v>16</v>
+      </c>
+      <c r="E18">
+        <v>19.5</v>
+      </c>
+      <c r="F18">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G18">
+        <v>4.82</v>
+      </c>
+      <c r="H18">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="I18">
+        <v>6.2300000000000003E-3</v>
+      </c>
+      <c r="J18">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K18">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18">
+        <v>12.9</v>
+      </c>
+      <c r="N18">
+        <v>13.58</v>
+      </c>
+      <c r="O18">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>3.04E-2</v>
+      </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>23.27</v>
+      </c>
+      <c r="F19">
+        <v>1.72</v>
+      </c>
+      <c r="G19">
+        <v>5.36</v>
+      </c>
+      <c r="H19">
+        <v>32.380000000000003</v>
+      </c>
+      <c r="I19">
+        <v>6.2300000000000003E-3</v>
+      </c>
+      <c r="J19">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K19">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19">
+        <v>12.9</v>
+      </c>
+      <c r="N19">
+        <v>13.58</v>
+      </c>
+      <c r="O19">
+        <v>3.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87E0E9C-6949-4238-A2BD-D62136568C91}">
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.1</v>
+      </c>
+      <c r="B2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C2">
+        <v>55</v>
+      </c>
+      <c r="D2">
+        <v>118</v>
+      </c>
+      <c r="E2">
+        <v>21.62</v>
+      </c>
+      <c r="F2">
+        <v>1.85</v>
+      </c>
+      <c r="G2">
+        <v>0.17</v>
+      </c>
+      <c r="H2">
+        <v>5.79</v>
+      </c>
+      <c r="I2">
+        <v>1.6100000000000001E-3</v>
+      </c>
+      <c r="J2">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K2">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>12.9</v>
+      </c>
+      <c r="N2">
+        <v>13.58</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.22</v>
+      </c>
+      <c r="B3">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="C3">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>110</v>
+      </c>
+      <c r="E3">
+        <v>20.82</v>
+      </c>
+      <c r="F3">
+        <v>1.92</v>
+      </c>
+      <c r="G3">
+        <v>0.92</v>
+      </c>
+      <c r="H3">
+        <v>53.68</v>
+      </c>
+      <c r="I3">
+        <v>1.6100000000000001E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K3">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>12.9</v>
+      </c>
+      <c r="N3">
+        <v>13.58</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.33</v>
+      </c>
+      <c r="B4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>23.12</v>
+      </c>
+      <c r="F4">
+        <v>1.73</v>
+      </c>
+      <c r="G4">
+        <v>0.95</v>
+      </c>
+      <c r="H4">
+        <v>32.5</v>
+      </c>
+      <c r="I4">
+        <v>1.6100000000000001E-3</v>
+      </c>
+      <c r="J4">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K4">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>12.9</v>
+      </c>
+      <c r="N4">
+        <v>13.58</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.47</v>
+      </c>
+      <c r="B5">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>38</v>
+      </c>
+      <c r="D5">
+        <v>65</v>
+      </c>
+      <c r="E5">
+        <v>21.82</v>
+      </c>
+      <c r="F5">
+        <v>1.83</v>
+      </c>
+      <c r="G5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>4.8300000000000001E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K5">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>12.9</v>
+      </c>
+      <c r="N5">
+        <v>13.58</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B6">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="C6">
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <v>55</v>
+      </c>
+      <c r="E6">
+        <v>20.57</v>
+      </c>
+      <c r="F6">
+        <v>1.94</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>23.04</v>
+      </c>
+      <c r="I6">
+        <v>4.3E-3</v>
+      </c>
+      <c r="J6">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K6">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>12.9</v>
+      </c>
+      <c r="N6">
+        <v>13.58</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.68</v>
+      </c>
+      <c r="B7">
+        <v>1.5E-3</v>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>54</v>
+      </c>
+      <c r="E7">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1.55</v>
+      </c>
+      <c r="H7">
+        <v>42.08</v>
+      </c>
+      <c r="I7">
+        <v>4.3E-3</v>
+      </c>
+      <c r="J7">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K7">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7">
+        <v>12.9</v>
+      </c>
+      <c r="N7">
+        <v>13.58</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.82</v>
+      </c>
+      <c r="B8">
+        <v>2E-3</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>18.03</v>
+      </c>
+      <c r="F8">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G8">
+        <v>2.06</v>
+      </c>
+      <c r="H8">
+        <v>57.33</v>
+      </c>
+      <c r="I8">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="J8">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>12.9</v>
+      </c>
+      <c r="N8">
+        <v>13.58</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>19.63</v>
+      </c>
+      <c r="F9">
+        <v>2.04</v>
+      </c>
+      <c r="G9">
+        <v>1.96</v>
+      </c>
+      <c r="H9">
+        <v>41.82</v>
+      </c>
+      <c r="I9">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K9">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9">
+        <v>12.9</v>
+      </c>
+      <c r="N9">
+        <v>13.58</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1.5</v>
+      </c>
+      <c r="B10">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="C10">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>19.27</v>
+      </c>
+      <c r="F10">
+        <v>2.08</v>
+      </c>
+      <c r="G10">
+        <v>2.88</v>
+      </c>
+      <c r="H10">
+        <v>60.16</v>
+      </c>
+      <c r="I10">
+        <v>3.0300000000000001E-3</v>
+      </c>
+      <c r="J10">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K10">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10">
+        <v>12.9</v>
+      </c>
+      <c r="N10">
+        <v>13.58</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>18.84</v>
+      </c>
+      <c r="F11">
+        <v>2.12</v>
+      </c>
+      <c r="G11">
+        <v>2.91</v>
+      </c>
+      <c r="H11">
+        <v>49.82</v>
+      </c>
+      <c r="I11">
+        <v>3.0300000000000001E-3</v>
+      </c>
+      <c r="J11">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K11">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11">
+        <v>12.9</v>
+      </c>
+      <c r="N11">
+        <v>13.58</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3.3</v>
+      </c>
+      <c r="B12">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2.9</v>
+      </c>
+      <c r="H12">
+        <v>41.87</v>
+      </c>
+      <c r="I12">
+        <v>3.0300000000000001E-3</v>
+      </c>
+      <c r="J12">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K12">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12">
+        <v>12.9</v>
+      </c>
+      <c r="N12">
+        <v>13.58</v>
+      </c>
+      <c r="O12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4.7</v>
+      </c>
+      <c r="B13">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>27</v>
+      </c>
+      <c r="E13">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="F13">
+        <v>2.13</v>
+      </c>
+      <c r="G13">
+        <v>4.49</v>
+      </c>
+      <c r="H13">
+        <v>65.069999999999993</v>
+      </c>
+      <c r="I13">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K13">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13">
+        <v>12.9</v>
+      </c>
+      <c r="N13">
+        <v>13.58</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>5.6</v>
+      </c>
+      <c r="B14">
+        <v>1.4E-2</v>
+      </c>
+      <c r="C14">
+        <v>11.5</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>18.72</v>
+      </c>
+      <c r="F14">
+        <v>2.14</v>
+      </c>
+      <c r="G14">
+        <v>5.19</v>
+      </c>
+      <c r="H14">
+        <v>55.68</v>
+      </c>
+      <c r="I14">
+        <v>2.1299999999999999E-3</v>
+      </c>
+      <c r="J14">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K14">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14">
+        <v>12.9</v>
+      </c>
+      <c r="N14">
+        <v>13.58</v>
+      </c>
+      <c r="O14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>6.8</v>
+      </c>
+      <c r="B15">
+        <v>1.54E-2</v>
+      </c>
+      <c r="C15">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F15">
+        <v>2.15</v>
+      </c>
+      <c r="G15">
+        <v>5.63</v>
+      </c>
+      <c r="H15">
+        <v>61.71</v>
+      </c>
+      <c r="I15">
+        <v>2.1299999999999999E-3</v>
+      </c>
+      <c r="J15">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15">
+        <v>12.9</v>
+      </c>
+      <c r="N15">
+        <v>13.58</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7.8</v>
+      </c>
+      <c r="B16">
+        <v>1.72E-2</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="F16">
+        <v>1.98</v>
+      </c>
+      <c r="G16">
+        <v>5.65</v>
+      </c>
+      <c r="H16">
+        <v>54.15</v>
+      </c>
+      <c r="I16">
+        <v>2.1299999999999999E-3</v>
+      </c>
+      <c r="J16">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K16">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16">
+        <v>12.9</v>
+      </c>
+      <c r="N16">
+        <v>13.58</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B17">
+        <v>1.89E-2</v>
+      </c>
+      <c r="C17">
+        <v>9.5</v>
+      </c>
+      <c r="D17">
+        <v>18</v>
+      </c>
+      <c r="E17">
+        <v>20.32</v>
+      </c>
+      <c r="F17">
+        <v>1.97</v>
+      </c>
+      <c r="G17">
+        <v>5.67</v>
+      </c>
+      <c r="H17">
+        <v>39.43</v>
+      </c>
+      <c r="I17">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="J17">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K17">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17">
+        <v>12.9</v>
+      </c>
+      <c r="N17">
+        <v>13.58</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>16</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>5.88</v>
+      </c>
+      <c r="H18">
+        <v>38.770000000000003</v>
+      </c>
+      <c r="I18">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="J18">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K18">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18">
+        <v>12.9</v>
+      </c>
+      <c r="N18">
+        <v>13.58</v>
+      </c>
+      <c r="O18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C19">
+        <v>8.25</v>
+      </c>
+      <c r="D19">
+        <v>14.5</v>
+      </c>
+      <c r="E19">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="F19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G19">
+        <v>5.69</v>
+      </c>
+      <c r="H19">
+        <v>34.19</v>
+      </c>
+      <c r="I19">
+        <v>6.9699999999999996E-3</v>
+      </c>
+      <c r="J19">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K19">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19">
+        <v>12.9</v>
+      </c>
+      <c r="N19">
+        <v>13.58</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6B4E82-5F29-4263-BF72-0349757B212F}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.22</v>
+      </c>
+      <c r="B2">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="C2">
+        <v>75</v>
+      </c>
+      <c r="D2">
+        <v>92</v>
+      </c>
+      <c r="E2">
+        <v>7.7</v>
+      </c>
+      <c r="F2">
+        <v>5.19</v>
+      </c>
+      <c r="G2">
+        <v>0.72</v>
+      </c>
+      <c r="H2">
+        <v>36.25</v>
+      </c>
+      <c r="I2">
+        <v>1.92E-3</v>
+      </c>
+      <c r="J2">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K2">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N2">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.33</v>
+      </c>
+      <c r="B3">
+        <v>1.16E-3</v>
+      </c>
+      <c r="C3">
+        <v>56</v>
+      </c>
+      <c r="D3">
+        <v>82</v>
+      </c>
+      <c r="E3">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="F3">
+        <v>4.2</v>
+      </c>
+      <c r="G3">
+        <v>1.61</v>
+      </c>
+      <c r="H3">
+        <v>90.56</v>
+      </c>
+      <c r="I3">
+        <v>1.5399999999999999E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K3">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N3">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.47</v>
+      </c>
+      <c r="B4">
+        <v>1.31E-3</v>
+      </c>
+      <c r="C4">
+        <v>49</v>
+      </c>
+      <c r="D4">
+        <v>77</v>
+      </c>
+      <c r="E4">
+        <v>11.02</v>
+      </c>
+      <c r="F4">
+        <v>3.63</v>
+      </c>
+      <c r="G4">
+        <v>1.51</v>
+      </c>
+      <c r="H4">
+        <v>55.6</v>
+      </c>
+      <c r="I4">
+        <v>4.6100000000000004E-3</v>
+      </c>
+      <c r="J4">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K4">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N4">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B5">
+        <v>1.4499999999999999E-3</v>
+      </c>
+      <c r="C5">
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>10.82</v>
+      </c>
+      <c r="F5">
+        <v>3.7</v>
+      </c>
+      <c r="G5">
+        <v>1.89</v>
+      </c>
+      <c r="H5">
+        <v>73.69</v>
+      </c>
+      <c r="I5">
+        <v>4.6100000000000004E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K5">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N5">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.68</v>
+      </c>
+      <c r="B6">
+        <v>1.9E-3</v>
+      </c>
+      <c r="C6">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>10.85</v>
+      </c>
+      <c r="F6">
+        <v>3.69</v>
+      </c>
+      <c r="G6">
+        <v>2.38</v>
+      </c>
+      <c r="H6">
+        <v>92.99</v>
+      </c>
+      <c r="I6">
+        <v>4.13E-3</v>
+      </c>
+      <c r="J6">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K6">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N6">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.82</v>
+      </c>
+      <c r="B7">
+        <v>2.1700000000000001E-3</v>
+      </c>
+      <c r="C7">
+        <v>38.5</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>10.78</v>
+      </c>
+      <c r="F7">
+        <v>3.71</v>
+      </c>
+      <c r="G7">
+        <v>1.92</v>
+      </c>
+      <c r="H7">
+        <v>48.88</v>
+      </c>
+      <c r="I7">
+        <v>4.13E-3</v>
+      </c>
+      <c r="J7">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K7">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N7">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>2.5300000000000001E-3</v>
+      </c>
+      <c r="C8">
+        <v>31.5</v>
+      </c>
+      <c r="D8">
+        <v>58</v>
+      </c>
+      <c r="E8">
+        <v>13.81</v>
+      </c>
+      <c r="F8">
+        <v>2.9</v>
+      </c>
+      <c r="G8">
+        <v>2.7</v>
+      </c>
+      <c r="H8">
+        <v>73.48</v>
+      </c>
+      <c r="I8">
+        <v>4.13E-3</v>
+      </c>
+      <c r="J8">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N8">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.5</v>
+      </c>
+      <c r="B9">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C9">
+        <v>23.5</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>13.95</v>
+      </c>
+      <c r="F9">
+        <v>2.87</v>
+      </c>
+      <c r="G9">
+        <v>3.3</v>
+      </c>
+      <c r="H9">
+        <v>63.42</v>
+      </c>
+      <c r="I9">
+        <v>3.31E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K9">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N9">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>15.74</v>
+      </c>
+      <c r="F10">
+        <v>2.54</v>
+      </c>
+      <c r="G10">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H10">
+        <v>80</v>
+      </c>
+      <c r="I10">
+        <v>2.97E-3</v>
+      </c>
+      <c r="J10">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K10">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N10">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3.3</v>
+      </c>
+      <c r="B11">
+        <v>9.0600000000000003E-3</v>
+      </c>
+      <c r="C11">
+        <v>18.5</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>11.18</v>
+      </c>
+      <c r="F11">
+        <v>3.58</v>
+      </c>
+      <c r="G11">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="H11">
+        <v>72.95</v>
+      </c>
+      <c r="I11">
+        <v>2.66E-3</v>
+      </c>
+      <c r="J11">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K11">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N11">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4.7</v>
+      </c>
+      <c r="B12">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>12.65</v>
+      </c>
+      <c r="F12">
+        <v>3.16</v>
+      </c>
+      <c r="G12">
+        <v>5.56</v>
+      </c>
+      <c r="H12">
+        <v>61.96</v>
+      </c>
+      <c r="I12">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J12">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K12">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N12">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5.6</v>
+      </c>
+      <c r="B13">
+        <v>1.34E-2</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>13.2</v>
+      </c>
+      <c r="F13">
+        <v>3.03</v>
+      </c>
+      <c r="G13">
+        <v>6.28</v>
+      </c>
+      <c r="H13">
+        <v>67.19</v>
+      </c>
+      <c r="I13">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K13">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N13">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6.8</v>
+      </c>
+      <c r="B14">
+        <v>1.52E-2</v>
+      </c>
+      <c r="C14">
+        <v>13.2</v>
+      </c>
+      <c r="D14">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>13.09</v>
+      </c>
+      <c r="F14">
+        <v>3.06</v>
+      </c>
+      <c r="G14">
+        <v>5.63</v>
+      </c>
+      <c r="H14">
+        <v>47.86</v>
+      </c>
+      <c r="I14">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J14">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K14">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N14">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B15">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="C15">
+        <v>11.5</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>15.6</v>
+      </c>
+      <c r="F15">
+        <v>2.56</v>
+      </c>
+      <c r="G15">
+        <v>6.89</v>
+      </c>
+      <c r="H15">
+        <v>60.83</v>
+      </c>
+      <c r="I15">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J15">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N15">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="C16">
+        <v>10.5</v>
+      </c>
+      <c r="D16">
+        <v>19.5</v>
+      </c>
+      <c r="E16">
+        <v>12.89</v>
+      </c>
+      <c r="F16">
+        <v>3.1</v>
+      </c>
+      <c r="G16">
+        <v>8.27</v>
+      </c>
+      <c r="H16">
+        <v>64.94</v>
+      </c>
+      <c r="I16">
+        <v>8.7200000000000003E-3</v>
+      </c>
+      <c r="J16">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K16">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N16">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>7.5</v>
+      </c>
+      <c r="E17">
+        <v>15.39</v>
+      </c>
+      <c r="F17">
+        <v>2.6</v>
+      </c>
+      <c r="G17">
+        <v>8.49</v>
+      </c>
+      <c r="H17">
+        <v>59.52</v>
+      </c>
+      <c r="I17">
+        <v>7.8499999999999993E-3</v>
+      </c>
+      <c r="J17">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K17">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N17">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="C18">
+        <v>7.2</v>
+      </c>
+      <c r="D18">
+        <v>6.2</v>
+      </c>
+      <c r="E18">
+        <v>15.66</v>
+      </c>
+      <c r="F18">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="G18">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="H18">
+        <v>50.87</v>
+      </c>
+      <c r="I18">
+        <v>7.0499999999999998E-3</v>
+      </c>
+      <c r="J18">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K18">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N18">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="C19">
+        <v>6.5</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>12.74</v>
+      </c>
+      <c r="F19">
+        <v>3.14</v>
+      </c>
+      <c r="G19">
+        <v>13.52</v>
+      </c>
+      <c r="H19">
+        <v>68.53</v>
+      </c>
+      <c r="I19">
+        <v>6.3E-3</v>
+      </c>
+      <c r="J19">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K19">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N19">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <v>9.8599999999999993E-2</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>4.3</v>
+      </c>
+      <c r="E20">
+        <v>14.06</v>
+      </c>
+      <c r="F20">
+        <v>2.84</v>
+      </c>
+      <c r="G20">
+        <v>14.3</v>
+      </c>
+      <c r="H20">
+        <v>53.92</v>
+      </c>
+      <c r="I20">
+        <v>5.6499999999999996E-3</v>
+      </c>
+      <c r="J20">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="K20">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N20">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O20">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DD2C18-56F6-488B-AE40-4C5FC864E9A0}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1.8600000000000001E-3</v>
+      </c>
+      <c r="C2">
+        <v>41</v>
+      </c>
+      <c r="D2">
+        <v>27.5</v>
+      </c>
+      <c r="E2">
+        <v>11.09</v>
+      </c>
+      <c r="F2">
+        <v>3.61</v>
+      </c>
+      <c r="G2">
+        <v>2.44</v>
+      </c>
+      <c r="H2">
+        <v>89.35</v>
+      </c>
+      <c r="I2">
+        <v>4.13E-3</v>
+      </c>
+      <c r="J2">
+        <v>1.173</v>
+      </c>
+      <c r="K2">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N2">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1.5</v>
+      </c>
+      <c r="B3">
+        <v>3.1199999999999999E-3</v>
+      </c>
+      <c r="C3">
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>11.56</v>
+      </c>
+      <c r="F3">
+        <v>3.46</v>
+      </c>
+      <c r="G3">
+        <v>3.05</v>
+      </c>
+      <c r="H3">
+        <v>75.73</v>
+      </c>
+      <c r="I3">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.173</v>
+      </c>
+      <c r="K3">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N3">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4">
+        <v>4.5700000000000003E-3</v>
+      </c>
+      <c r="C4">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>11.22</v>
+      </c>
+      <c r="F4">
+        <v>3.57</v>
+      </c>
+      <c r="G4">
+        <v>2.71</v>
+      </c>
+      <c r="H4">
+        <v>43.48</v>
+      </c>
+      <c r="I4">
+        <v>1.214E-2</v>
+      </c>
+      <c r="J4">
+        <v>1.173</v>
+      </c>
+      <c r="K4">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N4">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3.3</v>
+      </c>
+      <c r="B5">
+        <v>6.6400000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>20.5</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>12.42</v>
+      </c>
+      <c r="F5">
+        <v>3.22</v>
+      </c>
+      <c r="G5">
+        <v>3.67</v>
+      </c>
+      <c r="H5">
+        <v>50.78</v>
+      </c>
+      <c r="I5">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J5">
+        <v>1.173</v>
+      </c>
+      <c r="K5">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N5">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4.7</v>
+      </c>
+      <c r="B6">
+        <v>8.4700000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>12.63</v>
+      </c>
+      <c r="F6">
+        <v>3.17</v>
+      </c>
+      <c r="G6">
+        <v>4.09</v>
+      </c>
+      <c r="H6">
+        <v>44.05</v>
+      </c>
+      <c r="I6">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J6">
+        <v>1.173</v>
+      </c>
+      <c r="K6">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N6">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5.6</v>
+      </c>
+      <c r="B7">
+        <v>1.1089999999999999E-2</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>11.5</v>
+      </c>
+      <c r="E7">
+        <v>13.89</v>
+      </c>
+      <c r="F7">
+        <v>2.88</v>
+      </c>
+      <c r="G7">
+        <v>5.88</v>
+      </c>
+      <c r="H7">
+        <v>74.790000000000006</v>
+      </c>
+      <c r="I7">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J7">
+        <v>1.173</v>
+      </c>
+      <c r="K7">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N7">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6.8</v>
+      </c>
+      <c r="B8">
+        <v>1.2540000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>14.5</v>
+      </c>
+      <c r="D8">
+        <v>10.5</v>
+      </c>
+      <c r="E8">
+        <v>13.15</v>
+      </c>
+      <c r="F8">
+        <v>3.04</v>
+      </c>
+      <c r="G8">
+        <v>6.4</v>
+      </c>
+      <c r="H8">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="I8">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J8">
+        <v>1.173</v>
+      </c>
+      <c r="K8">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N8">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>1.72E-2</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>13.99</v>
+      </c>
+      <c r="F9">
+        <v>2.86</v>
+      </c>
+      <c r="G9">
+        <v>6.89</v>
+      </c>
+      <c r="H9">
+        <v>56.71</v>
+      </c>
+      <c r="I9">
+        <v>9.75E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.173</v>
+      </c>
+      <c r="K9">
+        <v>2.2130000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="N9">
+        <v>17.277000000000001</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038E82C3-370B-4F1B-939F-85E208A62757}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1350,2302 +5273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87E0E9C-6949-4238-A2BD-D62136568C91}">
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0.1</v>
-      </c>
-      <c r="B2">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="C2">
-        <v>55</v>
-      </c>
-      <c r="D2">
-        <v>118</v>
-      </c>
-      <c r="E2">
-        <v>21.62</v>
-      </c>
-      <c r="F2">
-        <v>1.85</v>
-      </c>
-      <c r="G2">
-        <v>0.17</v>
-      </c>
-      <c r="H2">
-        <v>5.79</v>
-      </c>
-      <c r="I2">
-        <v>1.6100000000000001E-3</v>
-      </c>
-      <c r="J2">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K2">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>12.9</v>
-      </c>
-      <c r="N2">
-        <v>13.58</v>
-      </c>
-      <c r="O2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.22</v>
-      </c>
-      <c r="B3">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="C3">
-        <v>51</v>
-      </c>
-      <c r="D3">
-        <v>110</v>
-      </c>
-      <c r="E3">
-        <v>20.82</v>
-      </c>
-      <c r="F3">
-        <v>1.92</v>
-      </c>
-      <c r="G3">
-        <v>0.92</v>
-      </c>
-      <c r="H3">
-        <v>53.68</v>
-      </c>
-      <c r="I3">
-        <v>1.6100000000000001E-3</v>
-      </c>
-      <c r="J3">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K3">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>12.9</v>
-      </c>
-      <c r="N3">
-        <v>13.58</v>
-      </c>
-      <c r="O3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0.33</v>
-      </c>
-      <c r="B4">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C4">
-        <v>42</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>23.12</v>
-      </c>
-      <c r="F4">
-        <v>1.73</v>
-      </c>
-      <c r="G4">
-        <v>0.95</v>
-      </c>
-      <c r="H4">
-        <v>32.5</v>
-      </c>
-      <c r="I4">
-        <v>1.6100000000000001E-3</v>
-      </c>
-      <c r="J4">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K4">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>12.9</v>
-      </c>
-      <c r="N4">
-        <v>13.58</v>
-      </c>
-      <c r="O4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.47</v>
-      </c>
-      <c r="B5">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C5">
-        <v>38</v>
-      </c>
-      <c r="D5">
-        <v>65</v>
-      </c>
-      <c r="E5">
-        <v>21.82</v>
-      </c>
-      <c r="F5">
-        <v>1.83</v>
-      </c>
-      <c r="G5">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="H5">
-        <v>29</v>
-      </c>
-      <c r="I5">
-        <v>4.8300000000000001E-3</v>
-      </c>
-      <c r="J5">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K5">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
-        <v>12.9</v>
-      </c>
-      <c r="N5">
-        <v>13.58</v>
-      </c>
-      <c r="O5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B6">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="C6">
-        <v>36</v>
-      </c>
-      <c r="D6">
-        <v>55</v>
-      </c>
-      <c r="E6">
-        <v>20.57</v>
-      </c>
-      <c r="F6">
-        <v>1.94</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>23.04</v>
-      </c>
-      <c r="I6">
-        <v>4.3E-3</v>
-      </c>
-      <c r="J6">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K6">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6">
-        <v>12.9</v>
-      </c>
-      <c r="N6">
-        <v>13.58</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>0.68</v>
-      </c>
-      <c r="B7">
-        <v>1.5E-3</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>54</v>
-      </c>
-      <c r="E7">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>1.55</v>
-      </c>
-      <c r="H7">
-        <v>42.08</v>
-      </c>
-      <c r="I7">
-        <v>4.3E-3</v>
-      </c>
-      <c r="J7">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K7">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7">
-        <v>12.9</v>
-      </c>
-      <c r="N7">
-        <v>13.58</v>
-      </c>
-      <c r="O7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>0.82</v>
-      </c>
-      <c r="B8">
-        <v>2E-3</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
-        <v>18.03</v>
-      </c>
-      <c r="F8">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="G8">
-        <v>2.06</v>
-      </c>
-      <c r="H8">
-        <v>57.33</v>
-      </c>
-      <c r="I8">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="J8">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K8">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>12.9</v>
-      </c>
-      <c r="N8">
-        <v>13.58</v>
-      </c>
-      <c r="O8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="C9">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>50</v>
-      </c>
-      <c r="E9">
-        <v>19.63</v>
-      </c>
-      <c r="F9">
-        <v>2.04</v>
-      </c>
-      <c r="G9">
-        <v>1.96</v>
-      </c>
-      <c r="H9">
-        <v>41.82</v>
-      </c>
-      <c r="I9">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="J9">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K9">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9">
-        <v>12.9</v>
-      </c>
-      <c r="N9">
-        <v>13.58</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1.5</v>
-      </c>
-      <c r="B10">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="C10">
-        <v>23</v>
-      </c>
-      <c r="D10">
-        <v>48</v>
-      </c>
-      <c r="E10">
-        <v>19.27</v>
-      </c>
-      <c r="F10">
-        <v>2.08</v>
-      </c>
-      <c r="G10">
-        <v>2.88</v>
-      </c>
-      <c r="H10">
-        <v>60.16</v>
-      </c>
-      <c r="I10">
-        <v>3.0300000000000001E-3</v>
-      </c>
-      <c r="J10">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K10">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10">
-        <v>12.9</v>
-      </c>
-      <c r="N10">
-        <v>13.58</v>
-      </c>
-      <c r="O10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B11">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>18.84</v>
-      </c>
-      <c r="F11">
-        <v>2.12</v>
-      </c>
-      <c r="G11">
-        <v>2.91</v>
-      </c>
-      <c r="H11">
-        <v>49.82</v>
-      </c>
-      <c r="I11">
-        <v>3.0300000000000001E-3</v>
-      </c>
-      <c r="J11">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K11">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11">
-        <v>12.9</v>
-      </c>
-      <c r="N11">
-        <v>13.58</v>
-      </c>
-      <c r="O11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>3.3</v>
-      </c>
-      <c r="B12">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-      <c r="D12">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>20.010000000000002</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>2.9</v>
-      </c>
-      <c r="H12">
-        <v>41.87</v>
-      </c>
-      <c r="I12">
-        <v>3.0300000000000001E-3</v>
-      </c>
-      <c r="J12">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K12">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12">
-        <v>12.9</v>
-      </c>
-      <c r="N12">
-        <v>13.58</v>
-      </c>
-      <c r="O12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>4.7</v>
-      </c>
-      <c r="B13">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="F13">
-        <v>2.13</v>
-      </c>
-      <c r="G13">
-        <v>4.49</v>
-      </c>
-      <c r="H13">
-        <v>65.069999999999993</v>
-      </c>
-      <c r="I13">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="J13">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K13">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13">
-        <v>12.9</v>
-      </c>
-      <c r="N13">
-        <v>13.58</v>
-      </c>
-      <c r="O13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>5.6</v>
-      </c>
-      <c r="B14">
-        <v>1.4E-2</v>
-      </c>
-      <c r="C14">
-        <v>11.5</v>
-      </c>
-      <c r="D14">
-        <v>22</v>
-      </c>
-      <c r="E14">
-        <v>18.72</v>
-      </c>
-      <c r="F14">
-        <v>2.14</v>
-      </c>
-      <c r="G14">
-        <v>5.19</v>
-      </c>
-      <c r="H14">
-        <v>55.68</v>
-      </c>
-      <c r="I14">
-        <v>2.1299999999999999E-3</v>
-      </c>
-      <c r="J14">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K14">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14">
-        <v>12.9</v>
-      </c>
-      <c r="N14">
-        <v>13.58</v>
-      </c>
-      <c r="O14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>6.8</v>
-      </c>
-      <c r="B15">
-        <v>1.54E-2</v>
-      </c>
-      <c r="C15">
-        <v>11</v>
-      </c>
-      <c r="D15">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F15">
-        <v>2.15</v>
-      </c>
-      <c r="G15">
-        <v>5.63</v>
-      </c>
-      <c r="H15">
-        <v>61.71</v>
-      </c>
-      <c r="I15">
-        <v>2.1299999999999999E-3</v>
-      </c>
-      <c r="J15">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K15">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15">
-        <v>12.9</v>
-      </c>
-      <c r="N15">
-        <v>13.58</v>
-      </c>
-      <c r="O15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>7.8</v>
-      </c>
-      <c r="B16">
-        <v>1.72E-2</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-      <c r="D16">
-        <v>18</v>
-      </c>
-      <c r="E16">
-        <v>20.149999999999999</v>
-      </c>
-      <c r="F16">
-        <v>1.98</v>
-      </c>
-      <c r="G16">
-        <v>5.65</v>
-      </c>
-      <c r="H16">
-        <v>54.15</v>
-      </c>
-      <c r="I16">
-        <v>2.1299999999999999E-3</v>
-      </c>
-      <c r="J16">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K16">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16">
-        <v>12.9</v>
-      </c>
-      <c r="N16">
-        <v>13.58</v>
-      </c>
-      <c r="O16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="B17">
-        <v>1.89E-2</v>
-      </c>
-      <c r="C17">
-        <v>9.5</v>
-      </c>
-      <c r="D17">
-        <v>18</v>
-      </c>
-      <c r="E17">
-        <v>20.32</v>
-      </c>
-      <c r="F17">
-        <v>1.97</v>
-      </c>
-      <c r="G17">
-        <v>5.67</v>
-      </c>
-      <c r="H17">
-        <v>39.43</v>
-      </c>
-      <c r="I17">
-        <v>7.8200000000000006E-3</v>
-      </c>
-      <c r="J17">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K17">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L17" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17">
-        <v>12.9</v>
-      </c>
-      <c r="N17">
-        <v>13.58</v>
-      </c>
-      <c r="O17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18">
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="C18">
-        <v>9</v>
-      </c>
-      <c r="D18">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>20</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>5.88</v>
-      </c>
-      <c r="H18">
-        <v>38.770000000000003</v>
-      </c>
-      <c r="I18">
-        <v>7.8200000000000006E-3</v>
-      </c>
-      <c r="J18">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K18">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18">
-        <v>12.9</v>
-      </c>
-      <c r="N18">
-        <v>13.58</v>
-      </c>
-      <c r="O18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="B19">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="C19">
-        <v>8.25</v>
-      </c>
-      <c r="D19">
-        <v>14.5</v>
-      </c>
-      <c r="E19">
-        <v>18.190000000000001</v>
-      </c>
-      <c r="F19">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G19">
-        <v>5.69</v>
-      </c>
-      <c r="H19">
-        <v>34.19</v>
-      </c>
-      <c r="I19">
-        <v>6.9699999999999996E-3</v>
-      </c>
-      <c r="J19">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K19">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19">
-        <v>12.9</v>
-      </c>
-      <c r="N19">
-        <v>13.58</v>
-      </c>
-      <c r="O19">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6B4E82-5F29-4263-BF72-0349757B212F}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="12" max="12" width="13.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0.22</v>
-      </c>
-      <c r="B2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="C2">
-        <v>75</v>
-      </c>
-      <c r="D2">
-        <v>92</v>
-      </c>
-      <c r="E2">
-        <v>7.7</v>
-      </c>
-      <c r="F2">
-        <v>5.19</v>
-      </c>
-      <c r="G2">
-        <v>0.72</v>
-      </c>
-      <c r="H2">
-        <v>36.25</v>
-      </c>
-      <c r="I2">
-        <v>1.92E-3</v>
-      </c>
-      <c r="J2">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K2">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N2">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.33</v>
-      </c>
-      <c r="B3">
-        <v>1.16E-3</v>
-      </c>
-      <c r="C3">
-        <v>56</v>
-      </c>
-      <c r="D3">
-        <v>82</v>
-      </c>
-      <c r="E3">
-        <v>9.5299999999999994</v>
-      </c>
-      <c r="F3">
-        <v>4.2</v>
-      </c>
-      <c r="G3">
-        <v>1.61</v>
-      </c>
-      <c r="H3">
-        <v>90.56</v>
-      </c>
-      <c r="I3">
-        <v>1.5399999999999999E-3</v>
-      </c>
-      <c r="J3">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K3">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N3">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0.47</v>
-      </c>
-      <c r="B4">
-        <v>1.31E-3</v>
-      </c>
-      <c r="C4">
-        <v>49</v>
-      </c>
-      <c r="D4">
-        <v>77</v>
-      </c>
-      <c r="E4">
-        <v>11.02</v>
-      </c>
-      <c r="F4">
-        <v>3.63</v>
-      </c>
-      <c r="G4">
-        <v>1.51</v>
-      </c>
-      <c r="H4">
-        <v>55.6</v>
-      </c>
-      <c r="I4">
-        <v>4.6100000000000004E-3</v>
-      </c>
-      <c r="J4">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K4">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N4">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B5">
-        <v>1.4499999999999999E-3</v>
-      </c>
-      <c r="C5">
-        <v>47</v>
-      </c>
-      <c r="D5">
-        <v>62</v>
-      </c>
-      <c r="E5">
-        <v>10.82</v>
-      </c>
-      <c r="F5">
-        <v>3.7</v>
-      </c>
-      <c r="G5">
-        <v>1.89</v>
-      </c>
-      <c r="H5">
-        <v>73.69</v>
-      </c>
-      <c r="I5">
-        <v>4.6100000000000004E-3</v>
-      </c>
-      <c r="J5">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K5">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N5">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>0.68</v>
-      </c>
-      <c r="B6">
-        <v>1.9E-3</v>
-      </c>
-      <c r="C6">
-        <v>41</v>
-      </c>
-      <c r="D6">
-        <v>60</v>
-      </c>
-      <c r="E6">
-        <v>10.85</v>
-      </c>
-      <c r="F6">
-        <v>3.69</v>
-      </c>
-      <c r="G6">
-        <v>2.38</v>
-      </c>
-      <c r="H6">
-        <v>92.99</v>
-      </c>
-      <c r="I6">
-        <v>4.13E-3</v>
-      </c>
-      <c r="J6">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K6">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N6">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>0.82</v>
-      </c>
-      <c r="B7">
-        <v>2.1700000000000001E-3</v>
-      </c>
-      <c r="C7">
-        <v>38.5</v>
-      </c>
-      <c r="D7">
-        <v>51</v>
-      </c>
-      <c r="E7">
-        <v>10.78</v>
-      </c>
-      <c r="F7">
-        <v>3.71</v>
-      </c>
-      <c r="G7">
-        <v>1.92</v>
-      </c>
-      <c r="H7">
-        <v>48.88</v>
-      </c>
-      <c r="I7">
-        <v>4.13E-3</v>
-      </c>
-      <c r="J7">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K7">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N7">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>2.5300000000000001E-3</v>
-      </c>
-      <c r="C8">
-        <v>31.5</v>
-      </c>
-      <c r="D8">
-        <v>58</v>
-      </c>
-      <c r="E8">
-        <v>13.81</v>
-      </c>
-      <c r="F8">
-        <v>2.9</v>
-      </c>
-      <c r="G8">
-        <v>2.7</v>
-      </c>
-      <c r="H8">
-        <v>73.48</v>
-      </c>
-      <c r="I8">
-        <v>4.13E-3</v>
-      </c>
-      <c r="J8">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K8">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N8">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1.5</v>
-      </c>
-      <c r="B9">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="C9">
-        <v>23.5</v>
-      </c>
-      <c r="D9">
-        <v>40</v>
-      </c>
-      <c r="E9">
-        <v>13.95</v>
-      </c>
-      <c r="F9">
-        <v>2.87</v>
-      </c>
-      <c r="G9">
-        <v>3.3</v>
-      </c>
-      <c r="H9">
-        <v>63.42</v>
-      </c>
-      <c r="I9">
-        <v>3.31E-3</v>
-      </c>
-      <c r="J9">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K9">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N9">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B10">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="C10">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>15.74</v>
-      </c>
-      <c r="F10">
-        <v>2.54</v>
-      </c>
-      <c r="G10">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="H10">
-        <v>80</v>
-      </c>
-      <c r="I10">
-        <v>2.97E-3</v>
-      </c>
-      <c r="J10">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K10">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N10">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>3.3</v>
-      </c>
-      <c r="B11">
-        <v>9.0600000000000003E-3</v>
-      </c>
-      <c r="C11">
-        <v>18.5</v>
-      </c>
-      <c r="D11">
-        <v>28</v>
-      </c>
-      <c r="E11">
-        <v>11.18</v>
-      </c>
-      <c r="F11">
-        <v>3.58</v>
-      </c>
-      <c r="G11">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="H11">
-        <v>72.95</v>
-      </c>
-      <c r="I11">
-        <v>2.66E-3</v>
-      </c>
-      <c r="J11">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K11">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N11">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>4.7</v>
-      </c>
-      <c r="B12">
-        <v>1.0699999999999999E-2</v>
-      </c>
-      <c r="C12">
-        <v>16</v>
-      </c>
-      <c r="D12">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>12.65</v>
-      </c>
-      <c r="F12">
-        <v>3.16</v>
-      </c>
-      <c r="G12">
-        <v>5.56</v>
-      </c>
-      <c r="H12">
-        <v>61.96</v>
-      </c>
-      <c r="I12">
-        <v>1.09E-2</v>
-      </c>
-      <c r="J12">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K12">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N12">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>5.6</v>
-      </c>
-      <c r="B13">
-        <v>1.34E-2</v>
-      </c>
-      <c r="C13">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>26</v>
-      </c>
-      <c r="E13">
-        <v>13.2</v>
-      </c>
-      <c r="F13">
-        <v>3.03</v>
-      </c>
-      <c r="G13">
-        <v>6.28</v>
-      </c>
-      <c r="H13">
-        <v>67.19</v>
-      </c>
-      <c r="I13">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J13">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K13">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N13">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>6.8</v>
-      </c>
-      <c r="B14">
-        <v>1.52E-2</v>
-      </c>
-      <c r="C14">
-        <v>13.2</v>
-      </c>
-      <c r="D14">
-        <v>21</v>
-      </c>
-      <c r="E14">
-        <v>13.09</v>
-      </c>
-      <c r="F14">
-        <v>3.06</v>
-      </c>
-      <c r="G14">
-        <v>5.63</v>
-      </c>
-      <c r="H14">
-        <v>47.86</v>
-      </c>
-      <c r="I14">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J14">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K14">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N14">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="B15">
-        <v>1.6799999999999999E-2</v>
-      </c>
-      <c r="C15">
-        <v>11.5</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>15.6</v>
-      </c>
-      <c r="F15">
-        <v>2.56</v>
-      </c>
-      <c r="G15">
-        <v>6.89</v>
-      </c>
-      <c r="H15">
-        <v>60.83</v>
-      </c>
-      <c r="I15">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J15">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K15">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N15">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <v>2.4400000000000002E-2</v>
-      </c>
-      <c r="C16">
-        <v>10.5</v>
-      </c>
-      <c r="D16">
-        <v>19.5</v>
-      </c>
-      <c r="E16">
-        <v>12.89</v>
-      </c>
-      <c r="F16">
-        <v>3.1</v>
-      </c>
-      <c r="G16">
-        <v>8.27</v>
-      </c>
-      <c r="H16">
-        <v>64.94</v>
-      </c>
-      <c r="I16">
-        <v>8.7200000000000003E-3</v>
-      </c>
-      <c r="J16">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K16">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N16">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>2.7799999999999998E-2</v>
-      </c>
-      <c r="C17">
-        <v>9</v>
-      </c>
-      <c r="D17">
-        <v>7.5</v>
-      </c>
-      <c r="E17">
-        <v>15.39</v>
-      </c>
-      <c r="F17">
-        <v>2.6</v>
-      </c>
-      <c r="G17">
-        <v>8.49</v>
-      </c>
-      <c r="H17">
-        <v>59.52</v>
-      </c>
-      <c r="I17">
-        <v>7.8499999999999993E-3</v>
-      </c>
-      <c r="J17">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K17">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L17" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N17">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>22</v>
-      </c>
-      <c r="B18">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="C18">
-        <v>7.2</v>
-      </c>
-      <c r="D18">
-        <v>6.2</v>
-      </c>
-      <c r="E18">
-        <v>15.66</v>
-      </c>
-      <c r="F18">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="G18">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="H18">
-        <v>50.87</v>
-      </c>
-      <c r="I18">
-        <v>7.0499999999999998E-3</v>
-      </c>
-      <c r="J18">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K18">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N18">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>33</v>
-      </c>
-      <c r="B19">
-        <v>6.4399999999999999E-2</v>
-      </c>
-      <c r="C19">
-        <v>6.5</v>
-      </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19">
-        <v>12.74</v>
-      </c>
-      <c r="F19">
-        <v>3.14</v>
-      </c>
-      <c r="G19">
-        <v>13.52</v>
-      </c>
-      <c r="H19">
-        <v>68.53</v>
-      </c>
-      <c r="I19">
-        <v>6.3E-3</v>
-      </c>
-      <c r="J19">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K19">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M19">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N19">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>47</v>
-      </c>
-      <c r="B20">
-        <v>9.8599999999999993E-2</v>
-      </c>
-      <c r="C20">
-        <v>5</v>
-      </c>
-      <c r="D20">
-        <v>4.3</v>
-      </c>
-      <c r="E20">
-        <v>14.06</v>
-      </c>
-      <c r="F20">
-        <v>2.84</v>
-      </c>
-      <c r="G20">
-        <v>14.3</v>
-      </c>
-      <c r="H20">
-        <v>53.92</v>
-      </c>
-      <c r="I20">
-        <v>5.6499999999999996E-3</v>
-      </c>
-      <c r="J20">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K20">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N20">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O20">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DD2C18-56F6-488B-AE40-4C5FC864E9A0}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1.8600000000000001E-3</v>
-      </c>
-      <c r="C2">
-        <v>41</v>
-      </c>
-      <c r="D2">
-        <v>27.5</v>
-      </c>
-      <c r="E2">
-        <v>11.09</v>
-      </c>
-      <c r="F2">
-        <v>3.61</v>
-      </c>
-      <c r="G2">
-        <v>2.44</v>
-      </c>
-      <c r="H2">
-        <v>89.35</v>
-      </c>
-      <c r="I2">
-        <v>4.13E-3</v>
-      </c>
-      <c r="J2">
-        <v>1.173</v>
-      </c>
-      <c r="K2">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N2">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1.5</v>
-      </c>
-      <c r="B3">
-        <v>3.1199999999999999E-3</v>
-      </c>
-      <c r="C3">
-        <v>31</v>
-      </c>
-      <c r="D3">
-        <v>21</v>
-      </c>
-      <c r="E3">
-        <v>11.56</v>
-      </c>
-      <c r="F3">
-        <v>3.46</v>
-      </c>
-      <c r="G3">
-        <v>3.05</v>
-      </c>
-      <c r="H3">
-        <v>75.73</v>
-      </c>
-      <c r="I3">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="J3">
-        <v>1.173</v>
-      </c>
-      <c r="K3">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N3">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B4">
-        <v>4.5700000000000003E-3</v>
-      </c>
-      <c r="C4">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>11.22</v>
-      </c>
-      <c r="F4">
-        <v>3.57</v>
-      </c>
-      <c r="G4">
-        <v>2.71</v>
-      </c>
-      <c r="H4">
-        <v>43.48</v>
-      </c>
-      <c r="I4">
-        <v>1.214E-2</v>
-      </c>
-      <c r="J4">
-        <v>1.173</v>
-      </c>
-      <c r="K4">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N4">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3.3</v>
-      </c>
-      <c r="B5">
-        <v>6.6400000000000001E-3</v>
-      </c>
-      <c r="C5">
-        <v>20.5</v>
-      </c>
-      <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>12.42</v>
-      </c>
-      <c r="F5">
-        <v>3.22</v>
-      </c>
-      <c r="G5">
-        <v>3.67</v>
-      </c>
-      <c r="H5">
-        <v>50.78</v>
-      </c>
-      <c r="I5">
-        <v>1.09E-2</v>
-      </c>
-      <c r="J5">
-        <v>1.173</v>
-      </c>
-      <c r="K5">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N5">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4.7</v>
-      </c>
-      <c r="B6">
-        <v>8.4700000000000001E-3</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>12.63</v>
-      </c>
-      <c r="F6">
-        <v>3.17</v>
-      </c>
-      <c r="G6">
-        <v>4.09</v>
-      </c>
-      <c r="H6">
-        <v>44.05</v>
-      </c>
-      <c r="I6">
-        <v>1.09E-2</v>
-      </c>
-      <c r="J6">
-        <v>1.173</v>
-      </c>
-      <c r="K6">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N6">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5.6</v>
-      </c>
-      <c r="B7">
-        <v>1.1089999999999999E-2</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>11.5</v>
-      </c>
-      <c r="E7">
-        <v>13.89</v>
-      </c>
-      <c r="F7">
-        <v>2.88</v>
-      </c>
-      <c r="G7">
-        <v>5.88</v>
-      </c>
-      <c r="H7">
-        <v>74.790000000000006</v>
-      </c>
-      <c r="I7">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J7">
-        <v>1.173</v>
-      </c>
-      <c r="K7">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N7">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6.8</v>
-      </c>
-      <c r="B8">
-        <v>1.2540000000000001E-2</v>
-      </c>
-      <c r="C8">
-        <v>14.5</v>
-      </c>
-      <c r="D8">
-        <v>10.5</v>
-      </c>
-      <c r="E8">
-        <v>13.15</v>
-      </c>
-      <c r="F8">
-        <v>3.04</v>
-      </c>
-      <c r="G8">
-        <v>6.4</v>
-      </c>
-      <c r="H8">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="I8">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J8">
-        <v>1.173</v>
-      </c>
-      <c r="K8">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N8">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>1.72E-2</v>
-      </c>
-      <c r="C9">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>13.99</v>
-      </c>
-      <c r="F9">
-        <v>2.86</v>
-      </c>
-      <c r="G9">
-        <v>6.89</v>
-      </c>
-      <c r="H9">
-        <v>56.71</v>
-      </c>
-      <c r="I9">
-        <v>9.75E-3</v>
-      </c>
-      <c r="J9">
-        <v>1.173</v>
-      </c>
-      <c r="K9">
-        <v>2.2130000000000001</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9">
-        <v>17.149999999999999</v>
-      </c>
-      <c r="N9">
-        <v>17.277000000000001</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA20032-AD86-4D0C-A130-052D48CD2066}">
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4035,7 +5663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD40DBBF-C265-41B5-BA39-4A3C6B2256A7}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4660,7 +6288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88465A8-38E8-4A91-B975-918BA28C0BDB}">
   <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5425,7 +7053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADB7DD5-72A9-4E6E-8E2C-799D430E5B8A}">
   <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6098,7 +7726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B9FD53-474B-46DB-9021-F132455C8D7C}">
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6911,7 +8539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EBFC29-66B2-4263-880A-84BA447E51B6}">
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7488,7 +9116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3DFCD4-B0E1-4E18-94F6-382EF5FDA4D2}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8327,910 +9955,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCC0EA7-1C1A-400A-B5A7-4CD8402EAE42}">
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0.1</v>
-      </c>
-      <c r="B2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="C2">
-        <v>43</v>
-      </c>
-      <c r="D2">
-        <v>84</v>
-      </c>
-      <c r="E2">
-        <v>23.43</v>
-      </c>
-      <c r="F2">
-        <v>1.71</v>
-      </c>
-      <c r="G2">
-        <v>0.09</v>
-      </c>
-      <c r="H2">
-        <v>2.38</v>
-      </c>
-      <c r="I2">
-        <v>1.2800000000000001E-3</v>
-      </c>
-      <c r="J2">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K2">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
-        <v>12.9</v>
-      </c>
-      <c r="N2">
-        <v>13.58</v>
-      </c>
-      <c r="O2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.15</v>
-      </c>
-      <c r="B3">
-        <v>1E-3</v>
-      </c>
-      <c r="C3">
-        <v>41</v>
-      </c>
-      <c r="D3">
-        <v>75</v>
-      </c>
-      <c r="E3">
-        <v>20.62</v>
-      </c>
-      <c r="F3">
-        <v>1.94</v>
-      </c>
-      <c r="G3">
-        <v>0.27</v>
-      </c>
-      <c r="H3">
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="I3">
-        <v>1.2800000000000001E-3</v>
-      </c>
-      <c r="J3">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K3">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>12.9</v>
-      </c>
-      <c r="N3">
-        <v>13.58</v>
-      </c>
-      <c r="O3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0.22</v>
-      </c>
-      <c r="B4">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C4">
-        <v>38.5</v>
-      </c>
-      <c r="D4">
-        <v>65</v>
-      </c>
-      <c r="E4">
-        <v>21.26</v>
-      </c>
-      <c r="F4">
-        <v>1.88</v>
-      </c>
-      <c r="G4">
-        <v>0.71</v>
-      </c>
-      <c r="H4">
-        <v>32.14</v>
-      </c>
-      <c r="I4">
-        <v>1.2800000000000001E-3</v>
-      </c>
-      <c r="J4">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K4">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
-        <v>12.9</v>
-      </c>
-      <c r="N4">
-        <v>13.58</v>
-      </c>
-      <c r="O4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.33</v>
-      </c>
-      <c r="B5">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="C5">
-        <v>36.5</v>
-      </c>
-      <c r="D5">
-        <v>62</v>
-      </c>
-      <c r="E5">
-        <v>20.010000000000002</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>0.8</v>
-      </c>
-      <c r="H5">
-        <v>23.86</v>
-      </c>
-      <c r="I5">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="J5">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K5">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5">
-        <v>12.9</v>
-      </c>
-      <c r="N5">
-        <v>13.58</v>
-      </c>
-      <c r="O5">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>0.47</v>
-      </c>
-      <c r="B6">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="C6">
-        <v>32</v>
-      </c>
-      <c r="D6">
-        <v>55</v>
-      </c>
-      <c r="E6">
-        <v>21.16</v>
-      </c>
-      <c r="F6">
-        <v>1.89</v>
-      </c>
-      <c r="G6">
-        <v>0.86</v>
-      </c>
-      <c r="H6">
-        <v>18.940000000000001</v>
-      </c>
-      <c r="I6">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="J6">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K6">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6">
-        <v>12.9</v>
-      </c>
-      <c r="N6">
-        <v>13.58</v>
-      </c>
-      <c r="O6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>0.6</v>
-      </c>
-      <c r="B7">
-        <v>1.8E-3</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>51</v>
-      </c>
-      <c r="E7">
-        <v>22.9</v>
-      </c>
-      <c r="F7">
-        <v>1.75</v>
-      </c>
-      <c r="G7">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="H7">
-        <v>25.74</v>
-      </c>
-      <c r="I7">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="J7">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K7">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7">
-        <v>12.9</v>
-      </c>
-      <c r="N7">
-        <v>13.58</v>
-      </c>
-      <c r="O7">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>0.68</v>
-      </c>
-      <c r="B8">
-        <v>2.3E-3</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>19.22</v>
-      </c>
-      <c r="F8">
-        <v>2.08</v>
-      </c>
-      <c r="G8">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H8">
-        <v>24.57</v>
-      </c>
-      <c r="I8">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="J8">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K8">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8">
-        <v>12.9</v>
-      </c>
-      <c r="N8">
-        <v>13.58</v>
-      </c>
-      <c r="O8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>0.82</v>
-      </c>
-      <c r="B9">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>44</v>
-      </c>
-      <c r="E9">
-        <v>21.33</v>
-      </c>
-      <c r="F9">
-        <v>1.88</v>
-      </c>
-      <c r="G9">
-        <v>1.51</v>
-      </c>
-      <c r="H9">
-        <v>35.19</v>
-      </c>
-      <c r="I9">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="J9">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K9">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9">
-        <v>12.9</v>
-      </c>
-      <c r="N9">
-        <v>13.58</v>
-      </c>
-      <c r="O9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>3.3E-3</v>
-      </c>
-      <c r="C10">
-        <v>24</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>18.239999999999998</v>
-      </c>
-      <c r="F10">
-        <v>2.19</v>
-      </c>
-      <c r="G10">
-        <v>1.32</v>
-      </c>
-      <c r="H10">
-        <v>21.69</v>
-      </c>
-      <c r="I10">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="J10">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K10">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10">
-        <v>12.9</v>
-      </c>
-      <c r="N10">
-        <v>13.58</v>
-      </c>
-      <c r="O10">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1.5</v>
-      </c>
-      <c r="B11">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="C11">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <v>18.829999999999998</v>
-      </c>
-      <c r="F11">
-        <v>2.12</v>
-      </c>
-      <c r="G11">
-        <v>2.25</v>
-      </c>
-      <c r="H11">
-        <v>38.6</v>
-      </c>
-      <c r="I11">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="J11">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K11">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11">
-        <v>12.9</v>
-      </c>
-      <c r="N11">
-        <v>13.58</v>
-      </c>
-      <c r="O11">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1.8</v>
-      </c>
-      <c r="B12">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="C12">
-        <v>16.5</v>
-      </c>
-      <c r="D12">
-        <v>30</v>
-      </c>
-      <c r="E12">
-        <v>19.59</v>
-      </c>
-      <c r="F12">
-        <v>2.04</v>
-      </c>
-      <c r="G12">
-        <v>1.55</v>
-      </c>
-      <c r="H12">
-        <v>14.19</v>
-      </c>
-      <c r="I12">
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="J12">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K12">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12">
-        <v>12.9</v>
-      </c>
-      <c r="N12">
-        <v>13.58</v>
-      </c>
-      <c r="O12">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B13">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="C13">
-        <v>16</v>
-      </c>
-      <c r="D13">
-        <v>29</v>
-      </c>
-      <c r="E13">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="F13">
-        <v>2.13</v>
-      </c>
-      <c r="G13">
-        <v>2.1</v>
-      </c>
-      <c r="H13">
-        <v>31.39</v>
-      </c>
-      <c r="I13">
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="J13">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K13">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L13" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13">
-        <v>12.9</v>
-      </c>
-      <c r="N13">
-        <v>13.58</v>
-      </c>
-      <c r="O13">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>3.3</v>
-      </c>
-      <c r="B14">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="C14">
-        <v>12</v>
-      </c>
-      <c r="D14">
-        <v>27</v>
-      </c>
-      <c r="E14">
-        <v>21.88</v>
-      </c>
-      <c r="F14">
-        <v>1.83</v>
-      </c>
-      <c r="G14">
-        <v>2.71</v>
-      </c>
-      <c r="H14">
-        <v>25.18</v>
-      </c>
-      <c r="I14">
-        <v>7.8200000000000006E-3</v>
-      </c>
-      <c r="J14">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K14">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14">
-        <v>12.9</v>
-      </c>
-      <c r="N14">
-        <v>13.58</v>
-      </c>
-      <c r="O14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>4.7</v>
-      </c>
-      <c r="B15">
-        <v>1.43E-2</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>24</v>
-      </c>
-      <c r="E15">
-        <v>24.24</v>
-      </c>
-      <c r="F15">
-        <v>1.65</v>
-      </c>
-      <c r="G15">
-        <v>3.51</v>
-      </c>
-      <c r="H15">
-        <v>28.52</v>
-      </c>
-      <c r="I15">
-        <v>7.8200000000000006E-3</v>
-      </c>
-      <c r="J15">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K15">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15">
-        <v>12.9</v>
-      </c>
-      <c r="N15">
-        <v>13.58</v>
-      </c>
-      <c r="O15">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>5.6</v>
-      </c>
-      <c r="B16">
-        <v>1.83E-2</v>
-      </c>
-      <c r="C16">
-        <v>9.5</v>
-      </c>
-      <c r="D16">
-        <v>19</v>
-      </c>
-      <c r="E16">
-        <v>20.99</v>
-      </c>
-      <c r="F16">
-        <v>1.91</v>
-      </c>
-      <c r="G16">
-        <v>4.33</v>
-      </c>
-      <c r="H16">
-        <v>34.659999999999997</v>
-      </c>
-      <c r="I16">
-        <v>6.9699999999999996E-3</v>
-      </c>
-      <c r="J16">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K16">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16">
-        <v>12.9</v>
-      </c>
-      <c r="N16">
-        <v>13.58</v>
-      </c>
-      <c r="O16">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>6.8</v>
-      </c>
-      <c r="B17">
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="C17">
-        <v>9</v>
-      </c>
-      <c r="D17">
-        <v>18</v>
-      </c>
-      <c r="E17">
-        <v>21.61</v>
-      </c>
-      <c r="F17">
-        <v>1.85</v>
-      </c>
-      <c r="G17">
-        <v>3.86</v>
-      </c>
-      <c r="H17">
-        <v>25.1</v>
-      </c>
-      <c r="I17">
-        <v>6.9699999999999996E-3</v>
-      </c>
-      <c r="J17">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K17">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17">
-        <v>12.9</v>
-      </c>
-      <c r="N17">
-        <v>13.58</v>
-      </c>
-      <c r="O17">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="B18">
-        <v>2.46E-2</v>
-      </c>
-      <c r="C18">
-        <v>8.5</v>
-      </c>
-      <c r="D18">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>19.5</v>
-      </c>
-      <c r="F18">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="G18">
-        <v>4.82</v>
-      </c>
-      <c r="H18">
-        <v>33.659999999999997</v>
-      </c>
-      <c r="I18">
-        <v>6.2300000000000003E-3</v>
-      </c>
-      <c r="J18">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K18">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18">
-        <v>12.9</v>
-      </c>
-      <c r="N18">
-        <v>13.58</v>
-      </c>
-      <c r="O18">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>10</v>
-      </c>
-      <c r="B19">
-        <v>3.04E-2</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>14</v>
-      </c>
-      <c r="E19">
-        <v>23.27</v>
-      </c>
-      <c r="F19">
-        <v>1.72</v>
-      </c>
-      <c r="G19">
-        <v>5.36</v>
-      </c>
-      <c r="H19">
-        <v>32.380000000000003</v>
-      </c>
-      <c r="I19">
-        <v>6.2300000000000003E-3</v>
-      </c>
-      <c r="J19">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="K19">
-        <v>2.1179999999999999</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19">
-        <v>12.9</v>
-      </c>
-      <c r="N19">
-        <v>13.58</v>
-      </c>
-      <c r="O19">
-        <v>3.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>